--- a/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/프로젝트명_용어사전.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/프로젝트명_용어사전.xlsx
@@ -693,14 +693,14 @@
         <sz val="8.0"/>
         <u/>
       </rPr>
-      <t>www.fixframe.co</t>
+      <t>www.empasy.io</t>
     </r>
     <r>
       <rPr>
         <rFont val="제네시스산스 Text"/>
         <sz val="8.0"/>
       </rPr>
-      <t>.kr을 생각하는 경우가 많은데요, 엄격히 말해 'www'는 호스트명이고 '</t>
+      <t>를 생각하는 경우가 많은데요, 엄격히 말해 'www'는 호스트명이고 '</t>
     </r>
     <r>
       <rPr>
@@ -708,7 +708,7 @@
         <sz val="8.0"/>
         <u/>
       </rPr>
-      <t>fixframe.co.kr</t>
+      <t>empasy.io</t>
     </r>
     <r>
       <rPr>

--- a/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/프로젝트명_용어사전.xlsx
+++ b/templates/000_pm_suite/01_프로젝트 관리/07_의사소통관리/프로젝트명_용어사전.xlsx
@@ -516,12 +516,12 @@
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI</t>
+          <t>한빛글로벌 SyncFlow AI</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>GRV-DEG-060</t>
+          <t>EMP-DEG-060</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SyncGuard AI 17개 테이블 및 화장품 광고표현 표준 단어/용어/도메인 정의</t>
+          <t>SyncFlow AI 17개 테이블 및 전장부품 구매계약표현 표준 단어/용어/도메인 정의</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SyncGuard AI 시스템 구축 기준 상세 작성</t>
+          <t>SyncFlow AI 시스템 구축 기준 상세 작성</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>영문+숫자 채번 (예: CLM202610160001)</t>
+          <t>영문+숫자 채번 (예: REV202610160001)</t>
         </is>
       </c>
       <c r="F2" s="7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>사람 이름, 제품명, 브랜드명 등</t>
+          <t>사람 이름, 제품명, 사업본부명 등</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>상세내용/문안</t>
+          <t>상세내용/계약조항</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>심의 원문, 판정 근거, 사유 설명</t>
+          <t>검증 원문, 판정 근거, 사유 설명</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>식약처 판례 및 규제 문장 pgvector 임베딩</t>
+          <t>공정위·표준원 판례 및 규제 문장 pgvector 임베딩</t>
         </is>
       </c>
     </row>
@@ -1151,17 +1151,17 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>심의</t>
+          <t>검증</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Claim Review</t>
+          <t>Spec Review</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>CLM</t>
+          <t>REV</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>제품 표시·광고 표현에 대한 적법성 사전 검토</t>
+          <t>구매계약·기술규격 표현에 대한 적법성 사전 검토</t>
         </is>
       </c>
     </row>
@@ -1198,14 +1198,14 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>마케터가 제출하는 심의 요청</t>
+          <t>구매담당자가 제출하는 검증 요청</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>시안</t>
+          <t>계약·도서</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1225,14 +1225,14 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>광고 상세페이지, 포스터, 이미지 등 원본 제작물</t>
+          <t>구매계약 기술시방서, 포스터, 이미지 등 원본 제작물</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>문안</t>
+          <t>계약조항</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>시안 내에서 추출된 단위 광고 문장</t>
+          <t>계약·도서 내에서 추출된 단위 구매계약 문장</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>광고 문안에 사용된 특정 단어 및 어구</t>
+          <t>구매계약 계약조항에 사용된 특정 단어 및 어구</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>AI 또는 RA 전문가가 내린 적합/부적합 결정</t>
+          <t>AI 또는 법무·QA 전문위원가 내린 적합/부적합 결정</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>법령 위반 또는 행정처분 발생 가능성</t>
+          <t>법령 위반 또는 시정명령·심결 발생 가능성</t>
         </is>
       </c>
     </row>
@@ -1414,14 +1414,14 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>위험 문안을 완화하거나 대체하는 추천 표현</t>
+          <t>위험 계약조항을 완화하거나 대체하는 추천 표현</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>실증</t>
+          <t>시험검증</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>효능 및 인체적용시험 관련 공식 입증 데이터</t>
+          <t>성능규격 및 공인신뢰성시험 관련 공식 입증 데이터</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>표시·광고 공정화법, 식약처 가이드라인 등 법적 기준</t>
+          <t>하도급거래 공정화법, 공정위·표준원 가이드라인 등 법적 기준</t>
         </is>
       </c>
     </row>
@@ -1495,14 +1495,14 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>화장품을 구성하는 원료 및 화학 성분</t>
+          <t>전장부품을 구성하는 원소재 및 화학 성분</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>배합</t>
+          <t>조성</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>화장품 제조 시 성분의 혼합 및 배합 비율</t>
+          <t>전장부품 제조 시 성분의 혼합 및 조성 비율</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>원료 배합의 최대 허용 기준치</t>
+          <t>원소재 조성의 최대 허용 기준치</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Expert / RA</t>
+          <t>Expert / QA</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>규제 대응 전문 지식을 보유한 RA 담당자</t>
+          <t>규제 대응 전문 지식을 보유한 법무·QA 담당자</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>주의 판정에 대해 마케터가 입증 자료를 제출함</t>
+          <t>주의 판정에 대해 구매담당자가 입증 자료를 제출함</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>시안 및 심의 결과의 변경 차수</t>
+          <t>계약·도서 및 검증 결과의 변경 차수</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>브랜드</t>
+          <t>사업본부</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>한빛글로벌 산하 화장품 브랜드 (루미에르 등)</t>
+          <t>한빛글로벌 산하 전장부품 사업본부 (전장시스템본부 등)</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>심의 대상이 되는 화장품 품목</t>
+          <t>검증 대상이 되는 전장부품 품목</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>업로드된 시안 파일 또는 생성된 PDF 리포트</t>
+          <t>업로드된 계약·도서 파일 또는 생성된 PDF 리포트</t>
         </is>
       </c>
     </row>
@@ -2129,12 +2129,12 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>심의의뢰ID</t>
+          <t>검증요청ID</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>CLM_REQ_ID</t>
+          <t>REV_REQ_ID</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -2159,19 +2159,19 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>광고 심의 의뢰 고유 식별 번호</t>
+          <t>계약·규격 검증 의뢰 고유 식별 번호</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>심의신청번호</t>
+          <t>검증신청번호</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>CLM_NO</t>
+          <t>REV_NO</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -2196,14 +2196,14 @@
       </c>
       <c r="G3" s="9" t="inlineStr">
         <is>
-          <t>업무용 채번 심의 번호 (CLM+날짜+순번)</t>
+          <t>업무용 채번 검증 번호 (REV+날짜+순번)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>브랜드코드</t>
+          <t>사업본부코드</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>한빛글로벌 브랜드 구분 코드</t>
+          <t>한빛글로벌 사업본부 구분 코드</t>
         </is>
       </c>
     </row>
@@ -2270,19 +2270,19 @@
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
-          <t>심의 대상 화장품 제품 정식 명칭</t>
+          <t>검증 대상 전장부품 제품 정식 명칭</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>심의제목</t>
+          <t>검증제목</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>CLM_TITLE</t>
+          <t>REV_TITLE</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>마케터가 입력한 심의 의뢰 건명</t>
+          <t>구매담당자가 입력한 검증 요청 건명</t>
         </is>
       </c>
     </row>
@@ -2344,19 +2344,19 @@
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>상세페이지, SNS, 옥외광고 등 매체 구분</t>
+          <t>물품공급계약서, 기술시방서, CAD 도면 등 매체 구분</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>심의진행상태코드</t>
+          <t>검증진행상태코드</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>CLM_STAT_CD</t>
+          <t>REV_STAT_CD</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -2462,7 +2462,7 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>시안파일ID</t>
+          <t>계약·도서파일ID</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -2492,14 +2492,14 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>MinIO 스토리지 원본 시안 파일 식별자</t>
+          <t>MinIO 스토리지 원본 계약·도서 파일 식별자</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>시안파일경로</t>
+          <t>계약·도서파일경로</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -2536,7 +2536,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>시안파일해시</t>
+          <t>계약·도서파일해시</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -2566,14 +2566,14 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>시안 원본 위변조 방지용 SHA-256 해시</t>
+          <t>계약·도서 원본 위변조 방지용 SHA-256 해시</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>문안문장ID</t>
+          <t>계약조항문장ID</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -2610,7 +2610,7 @@
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>문안순번</t>
+          <t>계약조항순번</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>시안 내 문장 등장 순서 번호</t>
+          <t>계약·도서 내 문장 등장 순서 번호</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>정제문안내용</t>
+          <t>정제계약조항내용</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>형태소 분석 및 특수문자 정제 후 문안</t>
+          <t>형태소 분석 및 특수문자 정제 후 계약조항</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>BBOX_C심의RD_VAL</t>
+          <t>BBOX_C검증RD_VAL</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>시안 이미지 상의 위치 좌표(x, y, w, h)</t>
+          <t>계약·도서 이미지 상의 위치 좌표(x, y, w, h)</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>1단계 금지어 룰사전 매칭 결과</t>
+          <t>1단계 독소조항 룰사전 매칭 결과</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>2단계 RAG로 매칭된 식약처 행정처분 번호</t>
+          <t>2단계 RAG로 매칭된 공정위·표준원 시정명령·심결 번호</t>
         </is>
       </c>
     </row>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>3단계 LLM Agent의 문맥 종합 심의 의견</t>
+          <t>3단계 LLM Agent의 문맥 종합 검증 의견</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>추천대체문안</t>
+          <t>추천표준수정조항</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
@@ -2936,14 +2936,14 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>AI가 제안한 식약처 승인 안전 대체 표현</t>
+          <t>AI가 제안한 공정위·표준원 승인 안전 대체 표현</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>대체문안적용여부</t>
+          <t>표준수정조항적용여부</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>마케터의 추천 대체 표현 채택 여부</t>
+          <t>구매담당자의 추천 대체 표현 채택 여부</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>RA 담당자의 AI 판정 수동 변경 여부</t>
+          <t>법무·QA 담당자의 AI 판정 수동 변경 여부</t>
         </is>
       </c>
     </row>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>RA 전문가의 최종 심의 및 소명 검토 의견</t>
+          <t>법무·QA 전문위원의 최종 검증 및 소명 검토 의견</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>실증자료ID</t>
+          <t>시험성적서ID</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
-          <t>ProductLab 연계 인체적용시험 보고서 ID</t>
+          <t>PLM-Nexus 연계 공인신뢰성시험 보고서 ID</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>전성분 RDB·ProductLab 원료 배합한도 기준 코드 ([Option] KT레몬 연동)</t>
+          <t>자재BOM RDB·PLM-Nexus 원소재 유해물질한도 기준 코드 ([Option] HB-Monitor 연동)</t>
         </is>
       </c>
     </row>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>심의를 신청한 마케터 사원번호</t>
+          <t>검증을 신청한 구매담당자 사원번호</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>심의자사원번호</t>
+          <t>검증자사원번호</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>심의를 확정한 RA 전문가 사원번호</t>
+          <t>검증을 확정한 법무·QA 전문위원 사원번호</t>
         </is>
       </c>
     </row>
